--- a/real votes.xlsx
+++ b/real votes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97252\Desktop\vote2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8605757-17A4-42BF-B8E7-27F789055498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84C5BF7-9548-459B-8FC3-BCAD165B1156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -463,41 +463,41 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F2" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G2" s="3">
         <v>10</v>
       </c>
       <c r="H2" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I2" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K2" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N2" s="3">
         <v>0</v>

--- a/real votes.xlsx
+++ b/real votes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97252\Desktop\vote2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84C5BF7-9548-459B-8FC3-BCAD165B1156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B848A691-D75E-4963-8A7B-90C0A3A3FA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -470,28 +470,28 @@
         <v>21</v>
       </c>
       <c r="D2" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H2" s="3">
         <v>7</v>
       </c>
       <c r="I2" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3">
         <v>6</v>

--- a/real votes.xlsx
+++ b/real votes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97252\Desktop\vote2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B848A691-D75E-4963-8A7B-90C0A3A3FA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C8041F-A301-45AA-91E7-121DD6AAD9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -470,13 +470,13 @@
         <v>21</v>
       </c>
       <c r="D2" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>12</v>
       </c>
       <c r="F2" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="3">
         <v>8</v>
@@ -491,13 +491,13 @@
         <v>7</v>
       </c>
       <c r="K2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3">
         <v>6</v>
       </c>
       <c r="M2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N2" s="3">
         <v>0</v>
